--- a/supplementary-materials/tables/Table_S11.xlsx
+++ b/supplementary-materials/tables/Table_S11.xlsx
@@ -82,7 +82,7 @@
     <t>Bernoulli(zp)</t>
   </si>
   <si>
-    <t>log recording effort + log anthropogenic-event rate + log frog-event rate + detection-level station intercept</t>
+    <t/>
   </si>
   <si>
     <t>All effort-confirmed days</t>
@@ -130,7 +130,7 @@
     <t>Derived posterior quantity</t>
   </si>
   <si>
-    <t>Draw-wise combination; new-site and new-day random effects integrated</t>
+    <t/>
   </si>
   <si>
     <t>Not a fitted response</t>
